--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Agota siempre la ventana completa de 1.5 s (CALYPSO_READ_WINDOW_MS).</t>
+          <t>OJO: NO ES UN TIEMPO DE LECTURA. El Calypso no esta conectado en C3, asi que los 1.500 s son el timeout completo de la ventana (CALYPSO_READ_WINDOW_MS) esperando datos que no llegan - rx=0 bytes. En un nodo con el sensor conectado este numero sera otro, y probablemente menor. Hasta entonces, el burst carga 3.0 s (16%) por un sensor ausente: sin el serian 16.29 s en vez de 19.29 s.</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>BURST=90</t>
+          <t>BURST=90. El sensor NO esta conectado en C3: el slot se ejecuta y agota su ventana, pero no mide nada (rx=0).</t>
         </is>
       </c>
     </row>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -728,7 +728,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>9 bursts, mediana; min 19.3 max 19.4 - muy estable</t>
+          <t>21 bursts, mediana; min 19.29 max 19.36. Identico en pre-alarma y en alarma: comparten rama de codigo</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo ALARMA = 25.5 s medidos entre bursts consecutivos; el nodo no duerme.</t>
+          <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo PRE-ALARMA y ALARMA = 25.5 s medidos entre bursts consecutivos; el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
         </is>
       </c>
       <c r="L2" s="22" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Periodo ALARMA (s)</t>
+          <t>Periodo PRE-ALARMA y ALARMA (s)</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Mediciones/h ALARMA</t>
+          <t>Mediciones/h PRE-ALARMA y ALARMA</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="6" t="n">
-        <v>19.3</v>
+        <v>20.26</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>21 bursts, mediana; min 19.29 max 19.36. Identico en pre-alarma y en alarma: comparten rama de codigo</t>
+          <t>13 bursts con el Calypso ya conectado (2026-10-07), mediana; min 18.53 max 20.37. Subio desde 19.29 s porque el CM1106 empeoro. Identico en pre-alarma y en alarma: comparten rama</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v>0.7</v>
       </c>
       <c r="C6" s="38" t="n">
-        <v>3.513</v>
+        <v>4.5</v>
       </c>
       <c r="D6" s="39">
         <f>IF(C6=0,0,C6/B6)</f>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>5x lo que dice la hoja. Incluye power-cycle y calentamiento: es un sensor de disparo unico, mide al alimentarse.</t>
+          <t>6.4x lo que dice la hoja, y EMPEORANDO: 3.513 s el 2026-10-06 y 4.500 s el 2026-10-07. Incluye power-cycle y calentamiento - es un sensor de disparo unico, mide al alimentarse. Ademas esta dando Timeout en 12 de cada 15 lecturas. Es el sensor con problema real del nodo.</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="38" t="n">
-        <v>2.114</v>
+        <v>2.116</v>
       </c>
       <c r="D7" s="39">
         <f>IF(C7=0,0,C7/B7)</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>OJO: NO ES UN TIEMPO DE LECTURA. El Calypso no esta conectado en C3, asi que los 1.500 s son el timeout completo de la ventana (CALYPSO_READ_WINDOW_MS) esperando datos que no llegan - rx=0 bytes. En un nodo con el sensor conectado este numero sera otro, y probablemente menor. Hasta entonces, el burst carga 3.0 s (16%) por un sensor ausente: sin el serian 16.29 s en vez de 19.29 s.</t>
+          <t>SIGUE SIN SER UN TIEMPO DE LECTURA. El Calypso se conecto el 2026-10-07 y el slot NO cambio: 1.500 s exactos, la ventana entera (CALYPSO_READ_WINDOW_MS). El estado paso de 'silent' a 'OK' y windValid a 1, pero el log sigue diciendo rx=0 - CERO BYTES recibidos. Asi que el sensor consta como valido sin que llegue nada por la UART, y los 1.500 s siguen siendo un timeout. El burst carga 3.0 s (15%) por una lectura que no se produce.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="M3" s="23" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 25.5 s.</t>
+          <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 26.5 s (13 bursts, 2026-10-07).</t>
         </is>
       </c>
     </row>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="6" t="n">
-        <v>20.26</v>
+        <v>18.57</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>13 bursts con el Calypso ya conectado (2026-10-07), mediana; min 18.53 max 20.37. Subio desde 19.29 s porque el CM1106 empeoro. Identico en pre-alarma y en alarma: comparten rama</t>
+          <t>11 bursts con el Calypso leyendo y el rail de 5V mantenido (2026-10-07). Bajo desde 19.29 s: el Calypso deja de agotar su ventana y el CM1106 recupera un segundo. Identico en pre-alarma y en alarma: comparten rama de codigo</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
         <v>0.7</v>
       </c>
       <c r="C6" s="38" t="n">
-        <v>4.5</v>
+        <v>3.513</v>
       </c>
       <c r="D6" s="39">
         <f>IF(C6=0,0,C6/B6)</f>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>6.4x lo que dice la hoja, y EMPEORANDO: 3.513 s el 2026-10-06 y 4.500 s el 2026-10-07. Incluye power-cycle y calentamiento - es un sensor de disparo unico, mide al alimentarse. Ademas esta dando Timeout en 12 de cada 15 lecturas. Es el sensor con problema real del nodo.</t>
+          <t>5x lo que dice la hoja. Incluye power-cycle y calentamiento: es un sensor de disparo unico, mide al alimentarse. Llego a 4.500 s mientras el rail de 5V se cortaba en cada transmision y volvio a 3.513 s al mantenerlo (TX_KEEP_5V_RAIL), asi que sufria lo mismo que el Calypso. Sigue dando Timeout a menudo: es el sensor con el problema real que queda en el nodo.</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="38" t="n">
-        <v>2.116</v>
+        <v>2.135</v>
       </c>
       <c r="D7" s="39">
         <f>IF(C7=0,0,C7/B7)</f>
@@ -1252,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="38" t="n">
-        <v>1.5</v>
+        <v>0.774</v>
       </c>
       <c r="D8" s="39">
         <f>IF(C8=0,0,C8/B8)</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>SIGUE SIN SER UN TIEMPO DE LECTURA. El Calypso se conecto el 2026-10-07 y el slot NO cambio: 1.500 s exactos, la ventana entera (CALYPSO_READ_WINDOW_MS). El estado paso de 'silent' a 'OK' y windValid a 1, pero el log sigue diciendo rx=0 - CERO BYTES recibidos. Asi que el sensor consta como valido sin que llegue nada por la UART, y los 1.500 s siguen siendo un timeout. El burst carga 3.0 s (15%) por una lectura que no se produce.</t>
+          <t>AHORA SI ES UN TIEMPO DE LECTURA. 0.774 s, con 27 bytes recibidos en las 11 de 11 lecturas. Antes daba 1.500 s clavados - la ventana entera - porque el rail de 5V se cortaba en cada transmision y el sensor no llegaba a emitir: recibia datos UNA vez tras el arranque y cero despues, mientras seguia publicando windValid=1 con el valor viejo. Con TX_KEEP_5V_RAIL lee en todos los ciclos y el slot baja 0.73 s.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo PRE-ALARMA y ALARMA = 25.5 s medidos entre bursts consecutivos; el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
+          <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo PRE-ALARMA y ALARMA = 24.9 s medidos entre bursts consecutivos (2026-10-07, con el Calypso leyendo y el rail de 5V mantenido); el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
         </is>
       </c>
       <c r="L2" s="22" t="inlineStr">
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="M3" s="23" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 26.5 s (13 bursts, 2026-10-07).</t>
+          <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 24.9 s (11 bursts, 2026-10-07, con TX_KEEP_5V_RAIL).</t>
         </is>
       </c>
     </row>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Glosario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Empieza aqui" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tiempos por sensor" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Periodos y mediciones" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Metodo" sheetId="5" state="visible" r:id="rId5"/>
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="0.00x"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +71,30 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -97,6 +119,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,15 +233,26 @@
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -597,6 +635,320 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="36" t="inlineStr">
+        <is>
+          <t>Modulo C: que mide, cada cuanto, y por que</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Esta hoja explica las otras. Si es la primera vez que ves este libro, leela entera: son cinco minutos y sin ella los numeros no significan nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="38" t="inlineStr">
+        <is>
+          <t>QUE ES EL MODULO C</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>En una frase</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Es una caja con cinco sensores que se deja en el monte para detectar un incendio antes de que sea grande. Mide temperatura, humedad, humo, gases y viento, y manda los datos por radio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="37.5" customHeight="1">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>Funciona con bateria</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Y esa es la restriccion que explica TODO lo demas. No hay enchufe en el monte, asi que el aparato pasa la mayor parte del tiempo APAGADO - dormido - y solo se despierta a ratos para medir. Cada decision de diseno sale de ahi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>Los cinco sensores</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>BME690: temperatura, humedad, presion y gases.  BMV080: particulas, o sea humo.  CM1106: CO2.  SEN0466: monoxido de carbono.  Calypso: viento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>EL TICK: LA UNIDAD DE TIEMPO</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>Que es un tick</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>UN DESPERTAR. El aparato duerme, se despierta, mira que le toca hacer, lo hace, y se vuelve a dormir. A cada una de esas veces la llamamos un tick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="37.5" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Por que se cuenta en ticks y no en minutos</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Porque mientras duerme no tiene reloj. Al despertar no sabe cuanto tiempo ha pasado, solo sabe contar cuantas veces se ha despertado. Asi que el programa no dice 'mide cada 15 minutos', dice 'mide cada 90 despertares'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="37.5" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>Cuanto dura un tick</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>EN EL PROGRAMA pone 10 segundos: es lo que se programa dormir. PERO EN LA REALIDAD son 17.8 segundos, porque ademas de dormir 10 s esta despierto unos 8 s haciendo el trabajo. Los 17.8 s estan medidos sobre la placa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="37.5" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Por que importa tanto</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Porque para pasar de 'cada 90 ticks' a minutos hay que multiplicar por 17.8, no por 10. Si se usa el 10, todos los periodos salen un 78% mas cortos de lo que son en realidad. Es el error mas comun al leer estas cifras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>LAS DOS CLASES DE LECTURA</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>No lee todo cada vez</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Hay dos tipos de lectura, y es importante no confundirlos porque van a ritmos muy distintos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>1. CENTINELA  (lectura barata)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Lee solo temperatura, humedad y presion. Es rapido y gasta poco. Se hace cada 3 ticks, o sea cada 53 segundos. Sirve para vigilar en continuo por si algo empieza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="37.5" customHeight="1">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>2. BURST  (lectura completa)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>'Burst' es el nombre que le pusimos en el programa; en castellano seria LECTURA COMPLETA. Lee LOS CINCO SENSORES, incluidos los caros. Se hace cada 90 ticks, o sea cada 26.7 minutos, y tarda 18.57 segundos durante los cuales el aparato esta despierto entero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>Por que no leerlo todo siempre</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Porque los sensores caros gastan mucho: el de humo enciende un laser que consume 68 mA, el de gases calienta una resistencia a 320 grados, y el de CO2 hay que apagarlo y encenderlo entero cada vez. Hacer eso cada minuto vaciaria la bateria sin detectar nada antes: el humo y el CO2 no cambian de un segundo a otro. La temperatura si puede subir rapido, y por eso esa si se vigila seguido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>LOS TRES ESTADOS</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Lo habitual. Duerme entre lectura y lectura, hace un centinela cada 53 s y una lectura completa cada 26.7 min. Esta despierto un 45% del tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="37.5" customHeight="1">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>PRE-ALARMA</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Algun sensor ha cruzado su umbral. DEJA DE DORMIR y mide sin parar: una lectura completa cada 24.9 segundos. Tiene 10 minutos para confirmar; si en ese rato la cosa no se calma, pasa a ALARMA, y si se calma vuelve a NORMAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="37.5" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>ALARMA</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Confirmado. Se comporta EXACTAMENTE IGUAL que la pre-alarma - mismo codigo, mismos tiempos - asi que en las tablas los dos estados comparten columna. Lo unico que cambia es lo que se avisa hacia arriba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>COMO LEER CADA HOJA</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr"/>
+    </row>
+    <row r="27" ht="37.5" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>Tiempos por sensor</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Cuanto ocupa cada sensor en una lectura completa. 'Activo' es lo que tarda el sensor en si; 'recuperacion' es la espera obligatoria despues, antes de arrancar el siguiente, para que no se solapen dos cargas. Las dos cuentan para la bateria, porque el aparato esta despierto durante ambas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>Periodos y mediciones</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Cada cuanto se mide cada cosa y cuantas veces por hora. Compara lo que decia la hoja original (columnas B y C) con lo medido (de la D en adelante). Mira el ejemplo resuelto del final de esa hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Las cuatro cifras que mas cambian respecto a la hoja original.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>Metodo</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Como se obtuvo cada numero, para que cualquiera pueda repetirlo y comprobarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="37.5" customHeight="1">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>Los colores</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>AZUL = medido sobre la placa, es un dato duro. NEGRO = calculado con una formula a partir de los azules. AMARILLO = las dos constantes medidas de las que depende todo lo demas; si se cambian, el libro entero se recalcula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>EN UNA LINEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="B34" s="41" t="inlineStr">
+        <is>
+          <t>El aparato duerme para ahorrar bateria y se despierta cada 17.8 segundos. Cada 3 despertares mira la temperatura; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -763,303 +1115,6 @@
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>El envio a Modulo A es el error mas grave de la hoja: asume 30 min y son ~65 s. Como la radio es la carga mayor, invalida los totales por hora.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Que es un TICK, y por que casi todo son 90</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="33" t="inlineStr">
-        <is>
-          <t>EL TICK</t>
-        </is>
-      </c>
-      <c r="B3" s="34" t="inlineStr"/>
-    </row>
-    <row r="4" ht="39" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
-        <is>
-          <t>Que es</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>La unidad del planificador del nodo. El Modulo C no corre en continuo: duerme en deep sleep, despierta, mira QUE toca hacer en ese despertar, lo hace, y vuelve a dormir. Cada despertar es UN TICK.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
-        <is>
-          <t>Por que en ticks y no en minutos</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Porque el nodo no tiene reloj fiable al otro lado del sueno. Lo unico que sobrevive al deep sleep son unos contadores en memoria RTC. Asi que el firmware no dice 'lee cada 15 minutos', dice 'lee cada 90 despertares'. Los contadores SON el reloj.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
-        <is>
-          <t>Tick nominal</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>10 s. Es SLEEP_CYCLE_SECONDS: lo que el nodo programa dormir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="39" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
-        <is>
-          <t>Tick REAL (medido)</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>17.8 s. El nodo duerme 10 s, pero ademas esta despierto ~8 s haciendo el trabajo del tick. 10 + 7.8 = 17.8 s de reloj de pared por tick. ESTE es el numero que hay que usar para pasar de ticks a minutos; usar 10 s subestima todos los periodos en un 78%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="35" t="inlineStr">
-        <is>
-          <t>Consecuencia</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>El nodo esta despierto el ~45% del tiempo. El deep sleep aporta mucho menos de lo que parece, porque el trabajo de cada tick dura casi tanto como el sueno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>LOS TRES CONTADORES</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
-        <is>
-          <t>SENSOR_READ = 3</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Cada 3 ticks (53 s reales) se leen solo los sensores BARATOS: BME690 temperatura, humedad y presion. Son los 'centinelas': vigilan en continuo por si algo empieza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
-        <is>
-          <t>BURST = 90</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Cada 90 ticks (26.7 min reales) se lee TODO, incluidos los caros. De ahi que casi toda la columna 'Ticks' ponga 90 - ver abajo el porque.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="39" customHeight="1">
-      <c r="A13" s="35" t="inlineStr">
-        <is>
-          <t>LORA_TRANS = 4</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Cada 4 ticks (71 s reales) el nodo transmite a Modulo B lo que tenga acumulado. No transmite cada lectura: agrupa. Con SENSOR_READ=3 y LORA_TRANS=4 salen 2 lecturas por paquete, que es lo que se ve en el log como 'batch of 2 readings'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39" customHeight="1">
-      <c r="A14" s="35" t="inlineStr">
-        <is>
-          <t>Se pueden cambiar en caliente</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>Los tres viven en memoria RTC y Modulo A los puede cambiar por comando (CFG,SENSOR_READ / CFG,BURST / CFG,INTERVAL) sin reprogramar la placa. El equilibrio entre latencia de deteccion y bateria se ajusta en campo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
-        <is>
-          <t>POR QUE 90 TICKS</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="35" t="inlineStr">
-        <is>
-          <t>Razon 1 - energia</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Los sensores del burst son los caros: el BMV080 enciende un laser de 68 mA, el BME690 calienta a 320 C, el CM1106 hay que apagarlo y encenderlo entero para que mida. El burst completo tiene al nodo despierto 19.3 s. Hacerlo cada 3 ticks en vez de cada 90 multiplicaria por 30 ese gasto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="39" customHeight="1">
-      <c r="A18" s="35" t="inlineStr">
-        <is>
-          <t>Razon 2 - fisica del fenomeno</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Las particulas y el CO2 cambian a la escala de un incendio que se propaga, no a la de segundos. Medirlos cada 30 s no detecta nada antes: solo gasta bateria. La temperatura y la humedad SI pueden cambiar rapido, y por eso esas van cada 3 ticks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39" customHeight="1">
-      <c r="A19" s="35" t="inlineStr">
-        <is>
-          <t>La idea de fondo</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Vigilancia barata en continuo (centinelas cada 53 s) + confirmacion cara de vez en cuando (burst cada 26.7 min). Y si los centinelas detectan algo, el nodo pasa a alarma y entonces hace el burst completo cada 25.5 s: 63 veces mas a menudo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="33" t="inlineStr">
-        <is>
-          <t>LAS COLUMNAS</t>
-        </is>
-      </c>
-      <c r="B21" s="34" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="35" t="inlineStr">
-        <is>
-          <t>Ticks</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Cuantos despertares pasan entre una lectura de ese sensor y la siguiente. 3 = centinela, 90 = burst, 'excluido' = no se lee nunca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="35" t="inlineStr">
-        <is>
-          <t>Periodo NORMAL (s)</t>
-        </is>
-      </c>
-      <c r="B23" s="5">
-        <f> Ticks x 17.8 s. El tiempo real entre dos lecturas de ese sensor.</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="35" t="inlineStr">
-        <is>
-          <t>Mediciones/h NORMAL</t>
-        </is>
-      </c>
-      <c r="B24" s="5">
-        <f> 3600 / Periodo. Cuantas veces por hora se mide esa magnitud.</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="35" t="inlineStr">
-        <is>
-          <t>Periodo ALARMA (s)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>25.5 s para todos. En alarma el nodo NO duerme: repite el burst completo sin parar, asi que el periodo ya no depende de ticks sino de lo que tarda el propio burst.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
-        <is>
-          <t>t activo MEDIDO (s)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Lo que ese sensor tiene ocupado al microcontrolador en cada lectura. Medido con millis() alrededor de su slot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="35" t="inlineStr">
-        <is>
-          <t>Recuperacion / hueco (s)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Tiempo de espera OBLIGATORIO despues del sensor, antes de arrancar el siguiente. Normalmente 1.5 s para que una carga deje de consumir antes de que empiece la siguiente. Tras el BME690 son 6.1 s porque hace falta un ciclo completo de alimentacion para que el BMV080 pueda arrancar despues del calentador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="35" t="inlineStr">
-        <is>
-          <t>Slot total (s)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>activo + recuperacion. Es el coste REAL en tiempo despierto, que es lo que consume bateria: el ESP32 esta tirando sus ~35 mA durante todo el slot, mida o espere.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>En una linea</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="46" customHeight="1">
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>Un tick son 17.8 s reales. Los sensores caros van cada 90 ticks (26.7 min) porque gastan mucho y porque el humo y el CO2 no cambian en segundos. Los baratos van cada 3 ticks (53 s) para vigilar en continuo. Si saltan, el nodo deja de dormir y lo mide todo cada 25.5 s.</t>
         </is>
       </c>
     </row>
@@ -1149,20 +1204,20 @@
           <t>BME690 (T/H/P + gas)</t>
         </is>
       </c>
-      <c r="B5" s="37" t="n">
+      <c r="B5" s="42" t="n">
         <v>10.8</v>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="43" t="n">
         <v>0.037</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="44">
         <f>IF(C5=0,0,C5/B5)</f>
         <v/>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="43" t="n">
         <v>6.101</v>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="42">
         <f>C5+E5</f>
         <v/>
       </c>
@@ -1182,20 +1237,20 @@
           <t>CM1106 (CO2)</t>
         </is>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="42" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="38" t="n">
+      <c r="C6" s="43" t="n">
         <v>3.513</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="44">
         <f>IF(C6=0,0,C6/B6)</f>
         <v/>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="43" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="42">
         <f>C6+E6</f>
         <v/>
       </c>
@@ -1215,20 +1270,20 @@
           <t>BMV080 (particulas)</t>
         </is>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="42" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="43" t="n">
         <v>2.135</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="44">
         <f>IF(C7=0,0,C7/B7)</f>
         <v/>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="43" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="42">
         <f>C7+E7</f>
         <v/>
       </c>
@@ -1248,20 +1303,20 @@
           <t>Calypso (viento)</t>
         </is>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="43" t="n">
         <v>0.774</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="44">
         <f>IF(C8=0,0,C8/B8)</f>
         <v/>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="43" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="42">
         <f>C8+E8</f>
         <v/>
       </c>
@@ -1281,20 +1336,20 @@
           <t>SEN0466 (CO)</t>
         </is>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="42" t="n">
         <v>210</v>
       </c>
-      <c r="C9" s="38" t="n">
+      <c r="C9" s="43" t="n">
         <v>0.024</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="44">
         <f>IF(C9=0,0,C9/B9)</f>
         <v/>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="43" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="42">
         <f>C9+E9</f>
         <v/>
       </c>
@@ -1315,16 +1370,16 @@
         </is>
       </c>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="40">
+      <c r="C10" s="45">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
       <c r="D10" s="18" t="n"/>
-      <c r="E10" s="40">
+      <c r="E10" s="45">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="45">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
@@ -1349,7 +1404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1457,7 +1512,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>BME690 T/H/P (centinela)</t>
+          <t>BME690 temp/humedad  (centinela)</t>
         </is>
       </c>
       <c r="B5" s="24" t="n">
@@ -1491,14 +1546,14 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>SENSOR_READ=3</t>
+          <t>SENSOR_READ=3. El centinela es la lectura barata que vigila en continuo.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>BME690 VOC / gas</t>
+          <t>BME690 gases  (lectura completa)</t>
         </is>
       </c>
       <c r="B6" s="24" t="n">
@@ -1539,7 +1594,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>CM1106 CO2</t>
+          <t>CM1106 CO2  (lectura completa)</t>
         </is>
       </c>
       <c r="B7" s="24" t="n">
@@ -1580,7 +1635,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>BMV080 particulas</t>
+          <t>BMV080 humo  (lectura completa)</t>
         </is>
       </c>
       <c r="B8" s="24" t="n">
@@ -1621,7 +1676,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Calypso viento</t>
+          <t>Calypso viento  (lectura completa)</t>
         </is>
       </c>
       <c r="B9" s="24" t="n">
@@ -1766,7 +1821,105 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="31" t="inlineStr">
+        <is>
+          <t>COMO SE LEE UNA FILA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Columnas B y C</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Lo que decia la hoja original. Estan solo para comparar; no son medidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>Ticks (columna D)</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>Cuantos despertares del aparato pasan entre una lectura de ese sensor y la siguiente. 3 = centinela (lo barato, cada rato); 90 = burst o lectura completa (todo, de tanto en tanto); 'excluido' = no se lee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>Periodo NORMAL (E)</t>
+        </is>
+      </c>
+      <c r="B18" s="33">
+        <f> Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Mediciones/h NORMAL (F)</t>
+        </is>
+      </c>
+      <c r="B19" s="33">
+        <f> 3600 segundos de una hora, divididos entre el periodo.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Periodo ALARMA (G)</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>24.9 s para todos. En alarma el aparato no duerme y repite la lectura completa sin parar, asi que ya no depende de los despertares. M3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Factor (columna I)</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>Cuantas veces mas a menudo se mide en alarma que en normal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>EJEMPLO: la fila del CO2</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>Pone ticks = 90. Entonces: 90 despertares x 17.8 s = 1602 s, que son 26.7 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1602 = 2.25 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B17:I17"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1792,96 +1945,96 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Modulo C nodo 3 (C3), MAC 28:84:85:6F:82:88. Fecha 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>t activo por sensor</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>Instrumentacion anadida al firmware: millis() alrededor de cada runSlot(), con una linea [t] por slot. Entorno medir-tiempos (SLEEP_ENABLED=0) para que cada pasada sea un burst completo y el puerto serie no desaparezca. 9 bursts; se toma la mediana.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>Tick real</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>Periodos normales</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real. NO por los 10 s nominales.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>Modo alarma</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 24.9 s (11 bursts, 2026-10-07, con TX_KEEP_5V_RAIL).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Intervalos entre publicaciones AT+QMTPUB a v1/gateway/telemetry en 9 capturas de Modulo B del 5 y 6 de octubre. Se descartan los huecos &lt;5 s (publicaciones consecutivas del mismo evento) y &gt;600 s (reconexiones). n=138.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Lo que NO se ha medido aqui</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Las corrientes. Requieren el PPK2 en el banco. Las medidas de corriente existentes estan en test_consumos/mediciones.csv, y dos contradicen la hoja: el SEN0466 consume 14.5 mA y no 5, y no tiene modo reposo (~15 mA siempre que este alimentado, no 0 uA).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Avisos</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 45% de duty solo el ESP son ~15 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
         </is>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="0.00x"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,12 +63,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="000000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -153,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,7 +176,7 @@
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -210,7 +204,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -233,24 +226,24 @@
     <xf numFmtId="167" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -635,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -643,29 +636,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="36" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>Modulo C: que mide, cada cuanto, y por que</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>Esta hoja explica las otras. Si es la primera vez que ves este libro, leela entera: son cinco minutos y sin ella los numeros no significan nada.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>QUE ES EL MODULO C</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr"/>
+      <c r="B4" s="38" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>En una frase</t>
         </is>
@@ -677,7 +670,7 @@
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>Funciona con bateria</t>
         </is>
@@ -689,7 +682,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>Los cinco sensores</t>
         </is>
@@ -701,15 +694,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>EL TICK: LA UNIDAD DE TIEMPO</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr"/>
+      <c r="B9" s="38" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>Que es un tick</t>
         </is>
@@ -721,7 +714,7 @@
       </c>
     </row>
     <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="39" t="inlineStr">
         <is>
           <t>Por que se cuenta en ticks y no en minutos</t>
         </is>
@@ -733,7 +726,7 @@
       </c>
     </row>
     <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="39" t="inlineStr">
         <is>
           <t>Cuanto dura un tick</t>
         </is>
@@ -745,7 +738,7 @@
       </c>
     </row>
     <row r="13" ht="37.5" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="39" t="inlineStr">
         <is>
           <t>Por que importa tanto</t>
         </is>
@@ -757,15 +750,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>LAS DOS CLASES DE LECTURA</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr"/>
+      <c r="B15" s="38" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="40" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>No lee todo cada vez</t>
         </is>
@@ -777,7 +770,7 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="40" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>1. CENTINELA  (lectura barata)</t>
         </is>
@@ -789,7 +782,7 @@
       </c>
     </row>
     <row r="18" ht="37.5" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
+      <c r="A18" s="39" t="inlineStr">
         <is>
           <t>2. BURST  (lectura completa)</t>
         </is>
@@ -801,7 +794,7 @@
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>Por que no leerlo todo siempre</t>
         </is>
@@ -813,15 +806,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="38" t="inlineStr">
+      <c r="A21" s="37" t="inlineStr">
         <is>
           <t>LOS TRES ESTADOS</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr"/>
+      <c r="B21" s="38" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="40" t="inlineStr">
+      <c r="A22" s="39" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -833,7 +826,7 @@
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1">
-      <c r="A23" s="40" t="inlineStr">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>PRE-ALARMA</t>
         </is>
@@ -845,7 +838,7 @@
       </c>
     </row>
     <row r="24" ht="37.5" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="39" t="inlineStr">
         <is>
           <t>ALARMA</t>
         </is>
@@ -857,82 +850,118 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="38" t="inlineStr">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>COMO LEER CADA HOJA</t>
         </is>
       </c>
-      <c r="B26" s="39" t="inlineStr"/>
-    </row>
-    <row r="27" ht="37.5" customHeight="1">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="39" t="inlineStr">
         <is>
           <t>Tiempos por sensor</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Cuanto ocupa cada sensor en una lectura completa. 'Activo' es lo que tarda el sensor en si; 'recuperacion' es la espera obligatoria despues, antes de arrancar el siguiente, para que no se solapen dos cargas. Las dos cuentan para la bateria, porque el aparato esta despierto durante ambas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="40" t="inlineStr">
+          <t>Cuanto ocupa cada sensor. Dos columnas: TIEMPO MEDIDO es lo que tarda el sensor en si, y ESPERA OBLIGATORIA es el tiempo PARADO que hay que dejar despues, antes de arrancar el siguiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="50" customHeight="1">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Por que hay que esperar</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Porque los sensores NO PUEDEN FUNCIONAR A LA VEZ: el consumo de dos a la vez hunde la alimentacion y la placa se reinicia - se midieron 31 reinicios leyendo en paralelo frente a 2 leyendo de uno en uno. Asi que se leen en fila india, dejando un hueco de 1.5 s entre uno y otro para que al primero le de tiempo a dejar de consumir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="37.5" customHeight="1">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>El caso del BME690: 6.1 s</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Despues de que su sensor de gases caliente a 320 grados, el sensor de humo NO ARRANCA si solo se espera - se probo con 0.25 s y con 1.5 s y no bastaba. Hay que CORTAR la alimentacion y volver a darla. Esos 6.1 s son ese corte mas los 5 s que el sensor de humo necesita para iniciarse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="37.5" customHeight="1">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>Y esto gasta bateria</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Aunque no se mida nada. El microcontrolador sigue despierto consumiendo sus ~35 mA. De los 18.57 s que dura una lectura completa, SOLO 7.2 s son medir: los otros 11.4 s son estas esperas. El 61% del gasto no es medicion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>Periodos y mediciones</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Cada cuanto se mide cada cosa y cuantas veces por hora. Compara lo que decia la hoja original (columnas B y C) con lo medido (de la D en adelante). Mira el ejemplo resuelto del final de esa hoja.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="40" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="39" t="inlineStr">
         <is>
           <t>Resumen</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Las cuatro cifras que mas cambian respecto a la hoja original.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="40" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>Metodo</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Como se obtuvo cada numero, para que cualquiera pueda repetirlo y comprobarlo.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="37.5" customHeight="1">
-      <c r="A31" s="40" t="inlineStr">
+    <row r="34" ht="37.5" customHeight="1">
+      <c r="A34" s="39" t="inlineStr">
         <is>
           <t>Los colores</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>AZUL = medido sobre la placa, es un dato duro. NEGRO = calculado con una formula a partir de los azules. AMARILLO = las dos constantes medidas de las que depende todo lo demas; si se cambian, el libro entero se recalcula.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="36" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>EN UNA LINEA</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="B34" s="41" t="inlineStr">
+    <row r="37" ht="42" customHeight="1">
+      <c r="B37" s="40" t="inlineStr">
         <is>
           <t>El aparato duerme para ahorrar bateria y se despierta cada 17.8 segundos. Cada 3 despertares mira la temperatura; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
         </is>
@@ -1114,7 +1143,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>El envio a Modulo A es el error mas grave de la hoja: asume 30 min y son ~65 s. Como la radio es la carga mayor, invalida los totales por hora.</t>
+          <t>El periodo de envio a Modulo A conviene revisarlo: medido son ~65 s. Como la radio es la carga mayor del nodo, es el dato que mas pesa en el consumo por hora.</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1181,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Medido con instrumentacion por slot anadida al firmware (entorno medir-tiempos). Medianas de 9 bursts. Identicos en modo normal y en alarma: el slot es el mismo.</t>
+          <t>Cuanto ocupa cada sensor en una lectura completa. TIEMPO MEDIDO es lo que tarda el sensor en si. ESPERA OBLIGATORIA es el tiempo parado que hay que dejar despues, antes de arrancar el siguiente: los sensores no pueden funcionar a la vez porque el consumo simultaneo reinicia la placa (se midieron 31 reinicios frente a 2). Las dos cuentan para la bateria, porque el microcontrolador esta despierto durante ambas.</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1193,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>t activo HOJA (s)</t>
+          <t>Tiempo HOJA (s)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>t activo MEDIDO (s)</t>
+          <t>Tiempo MEDIDO (s)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1179,17 +1208,17 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Recuperacion / hueco (s)</t>
+          <t>Espera obligatoria despues (s)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Slot total (s)</t>
+          <t>Coste total (s)</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>% del burst</t>
+          <t>% del total</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -1204,20 +1233,20 @@
           <t>BME690 (T/H/P + gas)</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n">
+      <c r="B5" s="41" t="n">
         <v>10.8</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="42" t="n">
         <v>0.037</v>
       </c>
-      <c r="D5" s="44">
+      <c r="D5" s="43">
         <f>IF(C5=0,0,C5/B5)</f>
         <v/>
       </c>
-      <c r="E5" s="43" t="n">
+      <c r="E5" s="42" t="n">
         <v>6.101</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="41">
         <f>C5+E5</f>
         <v/>
       </c>
@@ -1237,20 +1266,20 @@
           <t>CM1106 (CO2)</t>
         </is>
       </c>
-      <c r="B6" s="42" t="n">
+      <c r="B6" s="41" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="43" t="n">
+      <c r="C6" s="42" t="n">
         <v>3.513</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="43">
         <f>IF(C6=0,0,C6/B6)</f>
         <v/>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="41">
         <f>C6+E6</f>
         <v/>
       </c>
@@ -1270,20 +1299,20 @@
           <t>BMV080 (particulas)</t>
         </is>
       </c>
-      <c r="B7" s="42" t="n">
+      <c r="B7" s="41" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="42" t="n">
         <v>2.135</v>
       </c>
-      <c r="D7" s="44">
+      <c r="D7" s="43">
         <f>IF(C7=0,0,C7/B7)</f>
         <v/>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="42">
+      <c r="F7" s="41">
         <f>C7+E7</f>
         <v/>
       </c>
@@ -1303,20 +1332,20 @@
           <t>Calypso (viento)</t>
         </is>
       </c>
-      <c r="B8" s="42" t="n">
+      <c r="B8" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="43" t="n">
+      <c r="C8" s="42" t="n">
         <v>0.774</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="43">
         <f>IF(C8=0,0,C8/B8)</f>
         <v/>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="41">
         <f>C8+E8</f>
         <v/>
       </c>
@@ -1336,20 +1365,20 @@
           <t>SEN0466 (CO)</t>
         </is>
       </c>
-      <c r="B9" s="42" t="n">
+      <c r="B9" s="41" t="n">
         <v>210</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="42" t="n">
         <v>0.024</v>
       </c>
-      <c r="D9" s="44">
+      <c r="D9" s="43">
         <f>IF(C9=0,0,C9/B9)</f>
         <v/>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="41">
         <f>C9+E9</f>
         <v/>
       </c>
@@ -1370,16 +1399,16 @@
         </is>
       </c>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="45">
+      <c r="C10" s="44">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
       <c r="D10" s="18" t="n"/>
-      <c r="E10" s="45">
+      <c r="E10" s="44">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
@@ -1438,22 +1467,22 @@
           <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo PRE-ALARMA y ALARMA = 24.9 s medidos entre bursts consecutivos (2026-10-07, con el Calypso leyendo y el rail de 5V mantenido); el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
         </is>
       </c>
-      <c r="L2" s="22" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>Tick real (s)</t>
         </is>
       </c>
-      <c r="M2" s="23" t="n">
+      <c r="M2" s="22" t="n">
         <v>17.8</v>
       </c>
     </row>
     <row r="3">
-      <c r="L3" s="22" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>Ciclo alarma (s)</t>
         </is>
       </c>
-      <c r="M3" s="23" t="n">
+      <c r="M3" s="22" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -1515,28 +1544,28 @@
           <t>BME690 temp/humedad  (centinela)</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="24" t="n">
         <v>12</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="23">
         <f>D5*$M$2</f>
         <v/>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="24">
         <f>3600/E5</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="24">
         <f>3600/G5</f>
         <v/>
       </c>
@@ -1556,28 +1585,28 @@
           <t>BME690 gases  (lectura completa)</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="24" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="23">
         <f>D6*$M$2</f>
         <v/>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="24">
         <f>3600/E6</f>
         <v/>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="24">
         <f>3600/G6</f>
         <v/>
       </c>
@@ -1597,28 +1626,28 @@
           <t>CM1106 CO2  (lectura completa)</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="23">
         <f>D7*$M$2</f>
         <v/>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="24">
         <f>3600/E7</f>
         <v/>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="24">
         <f>3600/G7</f>
         <v/>
       </c>
@@ -1638,28 +1667,28 @@
           <t>BMV080 humo  (lectura completa)</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="24" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="23">
         <f>D8*$M$2</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <f>3600/E8</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <f>3600/G8</f>
         <v/>
       </c>
@@ -1679,26 +1708,26 @@
           <t>Calypso viento  (lectura completa)</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="23" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="23">
         <f>D9*$M$2</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <f>3600/E9</f>
         <v/>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="24">
         <f>3600/G9</f>
         <v/>
       </c>
@@ -1718,30 +1747,30 @@
           <t>SEN0466 CO</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>excluido</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>nunca</t>
         </is>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="24">
         <f>3600/G10</f>
         <v/>
       </c>
@@ -1766,19 +1795,19 @@
       <c r="D11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="23">
         <f>D11*$M$2</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="24">
         <f>3600/E11</f>
         <v/>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="23">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="24">
         <f>3600/G11</f>
         <v/>
       </c>
@@ -1798,17 +1827,17 @@
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n">
+      <c r="B13" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="28" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="18" t="n"/>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="29" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <f>3600/E13</f>
         <v/>
       </c>
@@ -1817,94 +1846,94 @@
       <c r="I13" s="18" t="n"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t>138 intervalos reales. mediana 65.4 s / media 61.7 / p25 41.6 / p75 71.6 / max 125. La hoja asume 30 min: 27x de error.</t>
+          <t>138 intervalos reales. mediana 65.4 s / media 61.7 / p25 41.6 / p75 71.6 / max 125. La hoja original indica 30 min.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>COMO SE LEE UNA FILA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>Columnas B y C</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="32" t="inlineStr">
         <is>
           <t>Lo que decia la hoja original. Estan solo para comparar; no son medidas.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>Ticks (columna D)</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="32" t="inlineStr">
         <is>
           <t>Cuantos despertares del aparato pasan entre una lectura de ese sensor y la siguiente. 3 = centinela (lo barato, cada rato); 90 = burst o lectura completa (todo, de tanto en tanto); 'excluido' = no se lee.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>Periodo NORMAL (E)</t>
         </is>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="32">
         <f> Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>Mediciones/h NORMAL (F)</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="32">
         <f> 3600 segundos de una hora, divididos entre el periodo.</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t>Periodo ALARMA (G)</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>24.9 s para todos. En alarma el aparato no duerme y repite la lectura completa sin parar, asi que ya no depende de los despertares. M3.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>Factor (columna I)</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr">
+      <c r="B21" s="32" t="inlineStr">
         <is>
           <t>Cuantas veces mas a menudo se mide en alarma que en normal.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="34" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>EJEMPLO: la fila del CO2</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Pone ticks = 90. Entonces: 90 despertares x 17.8 s = 1602 s, que son 26.7 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1602 = 2.25 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
         </is>
@@ -1945,96 +1974,96 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Modulo C nodo 3 (C3), MAC 28:84:85:6F:82:88. Fecha 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>t activo por sensor</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Instrumentacion anadida al firmware: millis() alrededor de cada runSlot(), con una linea [t] por slot. Entorno medir-tiempos (SLEEP_ENABLED=0) para que cada pasada sea un burst completo y el puerto serie no desaparezca. 9 bursts; se toma la mediana.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="32" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>Tick real</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>Periodos normales</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real. NO por los 10 s nominales.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="32" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>Modo alarma</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 24.9 s (11 bursts, 2026-10-07, con TX_KEEP_5V_RAIL).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Intervalos entre publicaciones AT+QMTPUB a v1/gateway/telemetry en 9 capturas de Modulo B del 5 y 6 de octubre. Se descartan los huecos &lt;5 s (publicaciones consecutivas del mismo evento) y &gt;600 s (reconexiones). n=138.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="32" t="inlineStr">
+      <c r="A9" s="31" t="inlineStr">
         <is>
           <t>Lo que NO se ha medido aqui</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>Las corrientes. Requieren el PPK2 en el banco. Las medidas de corriente existentes estan en test_consumos/mediciones.csv, y dos contradicen la hoja: el SEN0466 consume 14.5 mA y no 5, y no tiene modo reposo (~15 mA siempre que este alimentado, no 0 uA).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Avisos</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 45% de duty solo el ESP son ~15 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
         </is>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -1570,7 +1570,7 @@
         <v/>
       </c>
       <c r="I5" s="7">
-        <f>IF(F5=0,0,H5/F5)</f>
+        <f>IF(F5=0,"solo en alarma",H5/F5)</f>
         <v/>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
         <v/>
       </c>
       <c r="I6" s="7">
-        <f>IF(F6=0,0,H6/F6)</f>
+        <f>IF(F6=0,"solo en alarma",H6/F6)</f>
         <v/>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -1652,7 +1652,7 @@
         <v/>
       </c>
       <c r="I7" s="7">
-        <f>IF(F7=0,0,H7/F7)</f>
+        <f>IF(F7=0,"solo en alarma",H7/F7)</f>
         <v/>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1693,7 +1693,7 @@
         <v/>
       </c>
       <c r="I8" s="7">
-        <f>IF(F8=0,0,H8/F8)</f>
+        <f>IF(F8=0,"solo en alarma",H8/F8)</f>
         <v/>
       </c>
       <c r="J8" s="8" t="inlineStr">
@@ -1732,7 +1732,7 @@
         <v/>
       </c>
       <c r="I9" s="7">
-        <f>IF(F9=0,0,H9/F9)</f>
+        <f>IF(F9=0,"solo en alarma",H9/F9)</f>
         <v/>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1775,12 +1775,12 @@
         <v/>
       </c>
       <c r="I10" s="7">
-        <f>IF(F10=0,0,H10/F10)</f>
+        <f>IF(F10=0,"solo en alarma",H10/F10)</f>
         <v/>
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>En NORMAL sigue excluido: el sueno corta los railes y no puede acumular 210 s. En PRE-ALARMA y ALARMA el nodo no duerme, calienta una vez (~3.5 min) y ya mide.</t>
+          <t>EL CERO DE LA COLUMNA NORMAL ES CORRECTO, no un dato que falte. Este sensor necesita 210 s de alimentacion CONTINUA para estabilizarse, y en modo normal el aparato duerme entre lecturas - dormir lo apaga todo - asi que el periodo despierto mas largo son ~8 s. No es que sea lento: es imposible. En PRE-ALARMA y ALARMA el aparato no duerme nunca, calienta una sola vez (~3.5 min) y a partir de ahi mide en cada ciclo; verificado en la placa. Para que midiera tambien en normal habria que dejar el rail de 5V encendido durante el sueno, y el sensor no tiene modo reposo: ~15 mA permanentes medidos. Eso es una decision de bateria, no de firmware.</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         <v/>
       </c>
       <c r="I11" s="7">
-        <f>IF(F11=0,0,H11/F11)</f>
+        <f>IF(F11=0,"solo en alarma",H11/F11)</f>
         <v/>
       </c>
       <c r="J11" s="8" t="inlineStr">

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -1887,9 +1887,10 @@
           <t>Periodo NORMAL (E)</t>
         </is>
       </c>
-      <c r="B18" s="32">
-        <f> Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</f>
-        <v/>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Es Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
@@ -1898,9 +1899,10 @@
           <t>Mediciones/h NORMAL (F)</t>
         </is>
       </c>
-      <c r="B19" s="32">
-        <f> 3600 segundos de una hora, divididos entre el periodo.</f>
-        <v/>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>Son 3600 segundos de una hora, divididos entre el periodo.</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B8" s="9" t="n"/>
       <c r="C8" s="6" t="n">
-        <v>18.57</v>
+        <v>18.54</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ARREGLADO 2026-10-06. Antes no se leia NUNCA. Los 210 s son estabilizacion en frio, no lectura: una vez caliente lee en 24 ms. No podia calentarse porque cada transmision cortaba el rail de 5V; con TX_KEEP_5V_RAIL se mantiene y el sensor vive. Solo en prealarma y alarma, que es cuando el nodo no duerme.</t>
+          <t>MEDIDO 2026-10-08: 24 ms exactos, 16 de 16 lecturas, sin una sola desviacion. Los 210 s de la hoja original son la ESTABILIZACION EN FRIO, no la lectura. Antes no se leia nunca porque cada transmision cortaba el rail de 5V y el sensor no llegaba a acumular esos 210 s; con TX_KEEP_5V_RAIL el rail se mantiene y el sensor vive. Una vez caliente SIGUE caliente aunque el microcontrolador se reinicie, porque el rail no se apaga: en esta medida leyo ya desde el primer burst, a los 4.7 s. Solo en prealarma y alarma, que es cuando el nodo no duerme.</t>
         </is>
       </c>
     </row>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -1744,7 +1744,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SEN0466 CO</t>
+          <t>SEN0466 CO  (solo en alarma)</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>excluido</t>
+          <t>solo alarma</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>nunca</t>
+          <t>no se mide</t>
         </is>
       </c>
       <c r="F10" s="26" t="n">

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -209,12 +209,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -636,29 +630,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Modulo C: que mide, cada cuanto, y por que</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Esta hoja explica las otras. Si es la primera vez que ves este libro, leela entera: son cinco minutos y sin ella los numeros no significan nada.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>QUE ES EL MODULO C</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr"/>
+      <c r="B4" s="36" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>En una frase</t>
         </is>
@@ -670,7 +664,7 @@
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="37" t="inlineStr">
         <is>
           <t>Funciona con bateria</t>
         </is>
@@ -682,7 +676,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Los cinco sensores</t>
         </is>
@@ -694,15 +688,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>EL TICK: LA UNIDAD DE TIEMPO</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr"/>
+      <c r="B9" s="36" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Que es un tick</t>
         </is>
@@ -714,7 +708,7 @@
       </c>
     </row>
     <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>Por que se cuenta en ticks y no en minutos</t>
         </is>
@@ -726,7 +720,7 @@
       </c>
     </row>
     <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>Cuanto dura un tick</t>
         </is>
@@ -738,7 +732,7 @@
       </c>
     </row>
     <row r="13" ht="37.5" customHeight="1">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Por que importa tanto</t>
         </is>
@@ -750,15 +744,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="37" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>LAS DOS CLASES DE LECTURA</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr"/>
+      <c r="B15" s="36" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>No lee todo cada vez</t>
         </is>
@@ -770,7 +764,7 @@
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="39" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t>1. CENTINELA  (lectura barata)</t>
         </is>
@@ -782,7 +776,7 @@
       </c>
     </row>
     <row r="18" ht="37.5" customHeight="1">
-      <c r="A18" s="39" t="inlineStr">
+      <c r="A18" s="37" t="inlineStr">
         <is>
           <t>2. BURST  (lectura completa)</t>
         </is>
@@ -794,7 +788,7 @@
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="37" t="inlineStr">
         <is>
           <t>Por que no leerlo todo siempre</t>
         </is>
@@ -806,15 +800,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="37" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>LOS TRES ESTADOS</t>
         </is>
       </c>
-      <c r="B21" s="38" t="inlineStr"/>
+      <c r="B21" s="36" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="37" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -826,7 +820,7 @@
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="37" t="inlineStr">
         <is>
           <t>PRE-ALARMA</t>
         </is>
@@ -838,7 +832,7 @@
       </c>
     </row>
     <row r="24" ht="37.5" customHeight="1">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>ALARMA</t>
         </is>
@@ -850,15 +844,15 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>COMO LEER CADA HOJA</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr"/>
+      <c r="B26" s="36" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>Tiempos por sensor</t>
         </is>
@@ -870,7 +864,7 @@
       </c>
     </row>
     <row r="28" ht="50" customHeight="1">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="37" t="inlineStr">
         <is>
           <t>Por que hay que esperar</t>
         </is>
@@ -882,7 +876,7 @@
       </c>
     </row>
     <row r="29" ht="37.5" customHeight="1">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>El caso del BME690: 6.1 s</t>
         </is>
@@ -894,7 +888,7 @@
       </c>
     </row>
     <row r="30" ht="37.5" customHeight="1">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="37" t="inlineStr">
         <is>
           <t>Y esto gasta bateria</t>
         </is>
@@ -906,7 +900,7 @@
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="39" t="inlineStr">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>Periodos y mediciones</t>
         </is>
@@ -918,7 +912,7 @@
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="39" t="inlineStr">
+      <c r="A32" s="37" t="inlineStr">
         <is>
           <t>Resumen</t>
         </is>
@@ -930,7 +924,7 @@
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>Metodo</t>
         </is>
@@ -942,7 +936,7 @@
       </c>
     </row>
     <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="39" t="inlineStr">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>Los colores</t>
         </is>
@@ -954,14 +948,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>EN UNA LINEA</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>El aparato duerme para ahorrar bateria y se despierta cada 17.8 segundos. Cada 3 despertares mira la temperatura; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
         </is>
@@ -1233,20 +1227,20 @@
           <t>BME690 (T/H/P + gas)</t>
         </is>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="39" t="n">
         <v>10.8</v>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="40" t="n">
         <v>0.037</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="41">
         <f>IF(C5=0,0,C5/B5)</f>
         <v/>
       </c>
-      <c r="E5" s="42" t="n">
+      <c r="E5" s="40" t="n">
         <v>6.101</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="39">
         <f>C5+E5</f>
         <v/>
       </c>
@@ -1266,20 +1260,20 @@
           <t>CM1106 (CO2)</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="39" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="40" t="n">
         <v>3.513</v>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="41">
         <f>IF(C6=0,0,C6/B6)</f>
         <v/>
       </c>
-      <c r="E6" s="42" t="n">
+      <c r="E6" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="39">
         <f>C6+E6</f>
         <v/>
       </c>
@@ -1299,20 +1293,20 @@
           <t>BMV080 (particulas)</t>
         </is>
       </c>
-      <c r="B7" s="41" t="n">
+      <c r="B7" s="39" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="40" t="n">
         <v>2.135</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="41">
         <f>IF(C7=0,0,C7/B7)</f>
         <v/>
       </c>
-      <c r="E7" s="42" t="n">
+      <c r="E7" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="39">
         <f>C7+E7</f>
         <v/>
       </c>
@@ -1332,20 +1326,20 @@
           <t>Calypso (viento)</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="40" t="n">
         <v>0.774</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="41">
         <f>IF(C8=0,0,C8/B8)</f>
         <v/>
       </c>
-      <c r="E8" s="42" t="n">
+      <c r="E8" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="39">
         <f>C8+E8</f>
         <v/>
       </c>
@@ -1365,20 +1359,20 @@
           <t>SEN0466 (CO)</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="39" t="n">
         <v>210</v>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="40" t="n">
         <v>0.024</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="41">
         <f>IF(C9=0,0,C9/B9)</f>
         <v/>
       </c>
-      <c r="E9" s="42" t="n">
+      <c r="E9" s="40" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="39">
         <f>C9+E9</f>
         <v/>
       </c>
@@ -1399,16 +1393,16 @@
         </is>
       </c>
       <c r="B10" s="18" t="n"/>
-      <c r="C10" s="44">
+      <c r="C10" s="42">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
       <c r="D10" s="18" t="n"/>
-      <c r="E10" s="44">
+      <c r="E10" s="42">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="42">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
@@ -1744,7 +1738,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SEN0466 CO  (solo en alarma)</t>
+          <t>SEN0466 CO  (centinela, 24/7)</t>
         </is>
       </c>
       <c r="B10" s="23" t="n">
@@ -1753,18 +1747,16 @@
       <c r="C10" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>solo alarma</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>no se mide</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>0</v>
+      <c r="D10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="23">
+        <f>D10*$M$2</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>3600/E10</f>
+        <v/>
       </c>
       <c r="G10" s="23">
         <f>$M$3</f>
@@ -1780,7 +1772,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>EL CERO DE LA COLUMNA NORMAL ES CORRECTO, no un dato que falte. Este sensor necesita 210 s de alimentacion CONTINUA para estabilizarse, y en modo normal el aparato duerme entre lecturas - dormir lo apaga todo - asi que el periodo despierto mas largo son ~8 s. No es que sea lento: es imposible. En PRE-ALARMA y ALARMA el aparato no duerme nunca, calienta una sola vez (~3.5 min) y a partir de ahi mide en cada ciclo; verificado en la placa. Para que midiera tambien en normal habria que dejar el rail de 5V encendido durante el sueno, y el sensor no tiene modo reposo: ~15 mA permanentes medidos. Eso es una decision de bateria, no de firmware.</t>
+          <t>VA CABLEADO DIRECTO A CORRIENTE, saltandose el transistor del rail de 5V, asi que nunca pierde alimentacion. Sus 210 s de estabilizacion se pagan UNA VEZ al energizar la placa y a partir de ahi esta siempre caliente. Por eso se lee en el centinela junto al BME690, cada 3 ticks, que es lo que pide el documento de estrategia. Hasta el 2026-10-08 el firmware lo excluia del ciclo, suponiendo que compartia el rail conmutado.</t>
         </is>
       </c>
     </row>
@@ -1827,17 +1819,17 @@
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="26" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="18" t="n"/>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="27" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="26">
         <f>3600/E13</f>
         <v/>
       </c>
@@ -1851,91 +1843,91 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>COMO SE LEE UNA FILA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Columnas B y C</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Lo que decia la hoja original. Estan solo para comparar; no son medidas.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>Ticks (columna D)</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>Cuantos despertares del aparato pasan entre una lectura de ese sensor y la siguiente. 3 = centinela (lo barato, cada rato); 90 = burst o lectura completa (todo, de tanto en tanto); 'excluido' = no se lee.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t>Periodo NORMAL (E)</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>Es Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>Mediciones/h NORMAL (F)</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Son 3600 segundos de una hora, divididos entre el periodo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>Periodo ALARMA (G)</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>24.9 s para todos. En alarma el aparato no duerme y repite la lectura completa sin parar, asi que ya no depende de los despertares. M3.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>Factor (columna I)</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Cuantas veces mas a menudo se mide en alarma que en normal.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>EJEMPLO: la fila del CO2</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="32" t="inlineStr">
         <is>
           <t>Pone ticks = 90. Entonces: 90 despertares x 17.8 s = 1602 s, que son 26.7 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1602 = 2.25 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
         </is>
@@ -1976,96 +1968,96 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Modulo C nodo 3 (C3), MAC 28:84:85:6F:82:88. Fecha 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="31" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>t activo por sensor</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Instrumentacion anadida al firmware: millis() alrededor de cada runSlot(), con una linea [t] por slot. Entorno medir-tiempos (SLEEP_ENABLED=0) para que cada pasada sea un burst completo y el puerto serie no desaparezca. 9 bursts; se toma la mediana.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>Tick real</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Periodos normales</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real. NO por los 10 s nominales.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>Modo alarma</t>
         </is>
       </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 24.9 s (11 bursts, 2026-10-07, con TX_KEEP_5V_RAIL).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Intervalos entre publicaciones AT+QMTPUB a v1/gateway/telemetry en 9 capturas de Modulo B del 5 y 6 de octubre. Se descartan los huecos &lt;5 s (publicaciones consecutivas del mismo evento) y &gt;600 s (reconexiones). n=138.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>Lo que NO se ha medido aqui</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Las corrientes. Requieren el PPK2 en el banco. Las medidas de corriente existentes estan en test_consumos/mediciones.csv, y dos contradicen la hoja: el SEN0466 consume 14.5 mA y no 5, y no tiene modo reposo (~15 mA siempre que este alimentado, no 0 uA).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Avisos</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 45% de duty solo el ESP son ~15 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
         </is>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -173,7 +173,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>EN EL PROGRAMA pone 10 segundos: es lo que se programa dormir. PERO EN LA REALIDAD son 17.8 segundos, porque ademas de dormir 10 s esta despierto unos 8 s haciendo el trabajo. Los 17.8 s estan medidos sobre la placa.</t>
+          <t>EN EL PROGRAMA pone 10 segundos: es lo que se programa dormir. PERO EN LA REALIDAD son 18.8 segundos, porque ademas de dormir 10 s esta despierto unos 8.8 s haciendo el trabajo. Medido sobre la placa el 2026-10-08.</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Porque para pasar de 'cada 90 ticks' a minutos hay que multiplicar por 17.8, no por 10. Si se usa el 10, todos los periodos salen un 78% mas cortos de lo que son en realidad. Es el error mas comun al leer estas cifras.</t>
+          <t>Porque para pasar de 'cada 90 ticks' a minutos hay que multiplicar por 18.8, no por 10. Si se usa el 10, todos los periodos salen un 78% mas cortos de lo que son en realidad. Es el error mas comun al leer estas cifras.</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="37.5" customHeight="1">
       <c r="A17" s="37" t="inlineStr">
         <is>
           <t>1. CENTINELA  (lectura barata)</t>
@@ -771,7 +771,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Lee solo temperatura, humedad y presion. Es rapido y gasta poco. Se hace cada 3 ticks, o sea cada 53 segundos. Sirve para vigilar en continuo por si algo empieza.</t>
+          <t>Lee temperatura, humedad, presion y CO. Es rapido y gasta poco. Se hace cada 3 ticks, o sea cada 56 segundos. Sirve para vigilar en continuo por si algo empieza. El sensor de CO esta cableado directo a corriente - siempre encendido - asi que esta siempre listo.</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>'Burst' es el nombre que le pusimos en el programa; en castellano seria LECTURA COMPLETA. Lee LOS CINCO SENSORES, incluidos los caros. Se hace cada 90 ticks, o sea cada 26.7 minutos, y tarda 18.57 segundos durante los cuales el aparato esta despierto entero.</t>
+          <t>'Burst' es el nombre que le pusimos en el programa; en castellano seria LECTURA COMPLETA. Lee LOS CINCO SENSORES, incluidos los caros. Se hace cada 90 ticks, o sea cada 28.2 minutos, y tarda 18.57 segundos durante los cuales el aparato esta despierto entero.</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Lo habitual. Duerme entre lectura y lectura, hace un centinela cada 53 s y una lectura completa cada 26.7 min. Esta despierto un 45% del tiempo.</t>
+          <t>Lo habitual. Duerme entre lectura y lectura, hace un centinela cada 53 s y una lectura completa cada 28.2 min. Esta despierto un 47% del tiempo.</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
     <row r="37" ht="42" customHeight="1">
       <c r="B37" s="38" t="inlineStr">
         <is>
-          <t>El aparato duerme para ahorrar bateria y se despierta cada 17.8 segundos. Cada 3 despertares mira la temperatura; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
+          <t>El aparato duerme para ahorrar bateria y se despierta cada 18.8 segundos. Cada 3 despertares mira la temperatura y el CO; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>El dato que mas cambia el modelo: el tick real son 17.8 s, no los 10 s nominales.</t>
+          <t>El dato que mas cambia el modelo: el tick real son 18.8 s, no los 10 s nominales.</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>37 intervalos STAT-a-STAT en dos capturas independientes de Modulo B</t>
+          <t>11 intervalos STAT-a-STAT del 2026-10-08, con el SEN0466 ya leyendo en el centinela. Eran 17.8 s antes de activarlo: el CO cuesta 1 s por tick, y no por leer - son 24 ms - sino porque obliga a levantar el rail en ciclos que antes no lo levantaban.</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>17.8 s de tick menos 10 s de deep sleep = 7.8-8.1 s despierto</t>
+          <t>18.8 s de tick menos 10 s de sueno = 8.8 s despierto. El documento de estrategia del nodo presupone despertares de 40 ms: la lectura del sensor si los cumple, pero el despertar completo -levantar railes, inicializar, leer, transmitir si toca- son 8.8 s, unas 220 veces mas.</t>
         </is>
       </c>
     </row>
@@ -1110,27 +1110,22 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Envio B -&gt; Modulo A</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1800</v>
-      </c>
+          <t>TX de C3 a Modulo B</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
       <c r="C9" s="6" t="n">
-        <v>65.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E9" s="11">
-        <f>C9/B9</f>
-        <v/>
-      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>138 intervalos reales de publicacion a ThingsBoard, mediana</t>
+          <t>10 intervalos medidos el 2026-10-08. El envio de B a Modulo A es aparte: 65.4 s, n=138.</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1453,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Periodo NORMAL = n ticks x 17.8 s (tick real medido). Periodo PRE-ALARMA y ALARMA = 24.9 s medidos entre bursts consecutivos (2026-10-07, con el Calypso leyendo y el rail de 5V mantenido); el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
+          <t>Periodo NORMAL = n ticks x 18.8 s (tick real medido el 2026-10-08). Periodo PRE-ALARMA y ALARMA = 24.9 s medidos entre bursts consecutivos (2026-10-07, con el Calypso leyendo y el rail de 5V mantenido); el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
         </is>
       </c>
       <c r="L2" s="12" t="inlineStr">
@@ -1467,7 +1462,7 @@
         </is>
       </c>
       <c r="M2" s="22" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="3">
@@ -1881,7 +1876,7 @@
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>Es Ticks x 17.8 s. El 17.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</t>
+          <t>Es Ticks x 18.8 s. El 18.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1924,7 @@
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>Pone ticks = 90. Entonces: 90 despertares x 17.8 s = 1602 s, que son 26.7 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1602 = 2.25 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
+          <t>Pone ticks = 90. Entonces: 90 despertares x 18.8 s = 1692 s, que son 28.2 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1692 = 2.13 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1994,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s.</t>
+          <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s. Remedido a 18.8 s el 2026-10-08, al entrar el CO en el centinela.</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2006,7 @@
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real. NO por los 10 s nominales.</t>
+          <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real de 18.8 s. NO por los 10 s nominales.</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="B10" s="30" t="inlineStr">
         <is>
-          <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 45% de duty solo el ESP son ~15 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
+          <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 47% de duty solo el ESP son ~16 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
         </is>
       </c>
     </row>

--- a/notes/tiempos_medidos_ModuloC_v2.xlsx
+++ b/notes/tiempos_medidos_ModuloC_v2.xlsx
@@ -88,7 +88,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -98,11 +98,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -147,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,9 +168,6 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -189,35 +181,35 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -227,10 +219,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -239,12 +231,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -254,7 +246,7 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -630,29 +622,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>Modulo C: que mide, cada cuanto, y por que</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t>Esta hoja explica las otras. Si es la primera vez que ves este libro, leela entera: son cinco minutos y sin ella los numeros no significan nada.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>QUE ES EL MODULO C</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr"/>
+      <c r="B4" s="35" t="inlineStr"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>En una frase</t>
         </is>
@@ -664,7 +656,7 @@
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>Funciona con bateria</t>
         </is>
@@ -676,7 +668,7 @@
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>Los cinco sensores</t>
         </is>
@@ -688,15 +680,15 @@
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>EL TICK: LA UNIDAD DE TIEMPO</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr"/>
+      <c r="B9" s="35" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Que es un tick</t>
         </is>
@@ -708,7 +700,7 @@
       </c>
     </row>
     <row r="11" ht="37.5" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Por que se cuenta en ticks y no en minutos</t>
         </is>
@@ -720,7 +712,7 @@
       </c>
     </row>
     <row r="12" ht="37.5" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>Cuanto dura un tick</t>
         </is>
@@ -732,7 +724,7 @@
       </c>
     </row>
     <row r="13" ht="37.5" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>Por que importa tanto</t>
         </is>
@@ -744,15 +736,15 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>LAS DOS CLASES DE LECTURA</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr"/>
+      <c r="B15" s="35" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>No lee todo cada vez</t>
         </is>
@@ -764,7 +756,7 @@
       </c>
     </row>
     <row r="17" ht="37.5" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>1. CENTINELA  (lectura barata)</t>
         </is>
@@ -776,7 +768,7 @@
       </c>
     </row>
     <row r="18" ht="37.5" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>2. BURST  (lectura completa)</t>
         </is>
@@ -788,7 +780,7 @@
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Por que no leerlo todo siempre</t>
         </is>
@@ -800,15 +792,15 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>LOS TRES ESTADOS</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr"/>
+      <c r="B21" s="35" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="37" t="inlineStr">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -820,7 +812,7 @@
       </c>
     </row>
     <row r="23" ht="37.5" customHeight="1">
-      <c r="A23" s="37" t="inlineStr">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>PRE-ALARMA</t>
         </is>
@@ -832,7 +824,7 @@
       </c>
     </row>
     <row r="24" ht="37.5" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>ALARMA</t>
         </is>
@@ -844,15 +836,15 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>COMO LEER CADA HOJA</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr"/>
+      <c r="B26" s="35" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Tiempos por sensor</t>
         </is>
@@ -864,7 +856,7 @@
       </c>
     </row>
     <row r="28" ht="50" customHeight="1">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>Por que hay que esperar</t>
         </is>
@@ -876,7 +868,7 @@
       </c>
     </row>
     <row r="29" ht="37.5" customHeight="1">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>El caso del BME690: 6.1 s</t>
         </is>
@@ -888,7 +880,7 @@
       </c>
     </row>
     <row r="30" ht="37.5" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Y esto gasta bateria</t>
         </is>
@@ -900,7 +892,7 @@
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Periodos y mediciones</t>
         </is>
@@ -912,7 +904,7 @@
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Resumen</t>
         </is>
@@ -924,7 +916,7 @@
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>Metodo</t>
         </is>
@@ -936,7 +928,7 @@
       </c>
     </row>
     <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Los colores</t>
         </is>
@@ -948,14 +940,14 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t>EN UNA LINEA</t>
         </is>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>El aparato duerme para ahorrar bateria y se despierta cada 18.8 segundos. Cada 3 despertares mira la temperatura y el CO; cada 90 lo mide todo. Si algo cruza un umbral deja de dormir y lo mide todo cada 25 segundos.</t>
         </is>
@@ -972,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1071,7 +1063,7 @@
       </c>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="10" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -1081,62 +1073,141 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>18.8 s de tick menos 10 s de sueno = 8.8 s despierto. El documento de estrategia del nodo presupone despertares de 40 ms: la lectura del sensor si los cumple, pero el despertar completo -levantar railes, inicializar, leer, transmitir si toca- son 8.8 s, unas 220 veces mas.</t>
+          <t>MEDIDO DOS VECES POR CAMINOS DISTINTOS, y coinciden: 47% desde las tramas STAT por radio (18.8 s de tick menos 10 s de sueno) y 49% sondeando si el puerto USB del nodo existe, que aparece y desaparece al ritmo del sueno y sirve de cronometro externo sin tocar la placa. El documento de estrategia del nodo presupone despertares de 40 ms: la lectura del sensor si los cumple, pero el despertar completo -levantar railes, inicializar, leer, transmitir si toca- son 8.8 s, unas 220 veces mas.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Burst completo (5 sensores)</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
+          <t>Sueno profundo por tick</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="C8" s="6" t="n">
-        <v>18.54</v>
+        <v>10.2</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n"/>
+      <c r="E8" s="7">
+        <f>C8/B8</f>
+        <v/>
+      </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>11 bursts con el Calypso leyendo y el rail de 5V mantenido (2026-10-07). Bajo desde 19.29 s: el Calypso deja de agotar su ventana y el CM1106 recupera un segundo. Identico en pre-alarma y en alarma: comparten rama de codigo</t>
+          <t>Medido con el puerto USB como cronometro: los tramos en que el nodo desaparece duran 10.2-10.3 s, clavados. El sueno si cumple lo programado; lo que se desvia es el despertar.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>TX de C3 a Modulo B</t>
+          <t>Despertar vacio (nada que hacer)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>La mitad de los despertares no tienen trabajo: el nodo mira el contador, ve que no toca ni centinela ni transmitir, y se vuelve a dormir en 0.3 s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Despertar con trabajo</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E10" s="7">
+        <f>C10/B10</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>De 12 a 18 s segun lo que toque. Aqui esta la diferencia con el documento de estrategia, que presupone 40 ms: la LECTURA del sensor si los cumple, pero levantar railes, inicializar, leer, transmitir y volver a dormir son segundos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Burst completo (5 sensores)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>11 bursts con el Calypso leyendo y el rail de 5V mantenido (2026-10-07). Bajo desde 19.29 s: el Calypso deja de agotar su ventana y el CM1106 recupera un segundo. Identico en pre-alarma y en alarma: comparten rama de codigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>TX de C3 a Modulo B</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="6" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>10 intervalos medidos el 2026-10-08. El envio de B a Modulo A es aparte: 65.4 s, n=138.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>El periodo de envio a Modulo A conviene revisarlo: medido son ~65 s. Como la radio es la carga mayor del nodo, es el dato que mas pesa en el consumo por hora.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A14:F14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1222,24 +1293,24 @@
           <t>BME690 (T/H/P + gas)</t>
         </is>
       </c>
-      <c r="B5" s="39" t="n">
+      <c r="B5" s="38" t="n">
         <v>10.8</v>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="C5" s="39" t="n">
         <v>0.037</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="40">
         <f>IF(C5=0,0,C5/B5)</f>
         <v/>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="39" t="n">
         <v>6.101</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F5" s="38">
         <f>C5+E5</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <f>F5/$F$10</f>
         <v/>
       </c>
@@ -1255,24 +1326,24 @@
           <t>CM1106 (CO2)</t>
         </is>
       </c>
-      <c r="B6" s="39" t="n">
+      <c r="B6" s="38" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" s="40" t="n">
+      <c r="C6" s="39" t="n">
         <v>3.513</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <f>IF(C6=0,0,C6/B6)</f>
         <v/>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F6" s="38">
         <f>C6+E6</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="15">
         <f>F6/$F$10</f>
         <v/>
       </c>
@@ -1288,24 +1359,24 @@
           <t>BMV080 (particulas)</t>
         </is>
       </c>
-      <c r="B7" s="39" t="n">
+      <c r="B7" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="39" t="n">
         <v>2.135</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <f>IF(C7=0,0,C7/B7)</f>
         <v/>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="38">
         <f>C7+E7</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="15">
         <f>F7/$F$10</f>
         <v/>
       </c>
@@ -1321,24 +1392,24 @@
           <t>Calypso (viento)</t>
         </is>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="39" t="n">
         <v>0.774</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="40">
         <f>IF(C8=0,0,C8/B8)</f>
         <v/>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="38">
         <f>C8+E8</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="15">
         <f>F8/$F$10</f>
         <v/>
       </c>
@@ -1354,24 +1425,24 @@
           <t>SEN0466 (CO)</t>
         </is>
       </c>
-      <c r="B9" s="39" t="n">
+      <c r="B9" s="38" t="n">
         <v>210</v>
       </c>
-      <c r="C9" s="40" t="n">
+      <c r="C9" s="39" t="n">
         <v>0.024</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="40">
         <f>IF(C9=0,0,C9/B9)</f>
         <v/>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="38">
         <f>C9+E9</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="15">
         <f>F9/$F$10</f>
         <v/>
       </c>
@@ -1382,30 +1453,30 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>TOTAL burst</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="42">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="41">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="18" t="n"/>
-      <c r="E10" s="42">
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="41">
         <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="19">
         <f>F10/$F$10</f>
         <v/>
       </c>
-      <c r="H10" s="21" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>Medido directamente: mediana 19.3 s (min 19.3, max 19.4, n=9). La suma de los slots lo reproduce.</t>
         </is>
@@ -1456,22 +1527,22 @@
           <t>Periodo NORMAL = n ticks x 18.8 s (tick real medido el 2026-10-08). Periodo PRE-ALARMA y ALARMA = 24.9 s medidos entre bursts consecutivos (2026-10-07, con el Calypso leyendo y el rail de 5V mantenido); el nodo no duerme. LOS DOS ESTADOS COMPARTEN CODIGO: la rama es if (g_alarmState &gt;= ALARM_PREALARM), con el mismo burst, el mismo gap de TX y el mismo hueco de muestreo, asi que sus tiempos son identicos y no hay que medirlos por separado. Lo unico propio de pre-alarma es el contador de su ventana de 10 min.</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>Tick real (s)</t>
         </is>
       </c>
-      <c r="M2" s="22" t="n">
+      <c r="M2" s="21" t="n">
         <v>18.8</v>
       </c>
     </row>
     <row r="3">
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>Ciclo alarma (s)</t>
         </is>
       </c>
-      <c r="M3" s="22" t="n">
+      <c r="M3" s="21" t="n">
         <v>24.9</v>
       </c>
     </row>
@@ -1533,28 +1604,28 @@
           <t>BME690 temp/humedad  (centinela)</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="23" t="n">
         <v>12</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <f>D5*$M$2</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="23">
         <f>3600/E5</f>
         <v/>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="23">
         <f>3600/G5</f>
         <v/>
       </c>
@@ -1574,28 +1645,28 @@
           <t>BME690 gases  (lectura completa)</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="23" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <f>D6*$M$2</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="23">
         <f>3600/E6</f>
         <v/>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="23">
         <f>3600/G6</f>
         <v/>
       </c>
@@ -1615,28 +1686,28 @@
           <t>CM1106 CO2  (lectura completa)</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="23" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <f>D7*$M$2</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="23">
         <f>3600/E7</f>
         <v/>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="23">
         <f>3600/G7</f>
         <v/>
       </c>
@@ -1656,28 +1727,28 @@
           <t>BMV080 humo  (lectura completa)</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="23" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="22">
         <f>D8*$M$2</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="23">
         <f>3600/E8</f>
         <v/>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="23">
         <f>3600/G8</f>
         <v/>
       </c>
@@ -1697,26 +1768,26 @@
           <t>Calypso viento  (lectura completa)</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="22" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="22">
         <f>D9*$M$2</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="23">
         <f>3600/E9</f>
         <v/>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="23">
         <f>3600/G9</f>
         <v/>
       </c>
@@ -1736,28 +1807,28 @@
           <t>SEN0466 CO  (centinela, 24/7)</t>
         </is>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="23" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f>D10*$M$2</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="23">
         <f>3600/E10</f>
         <v/>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="23">
         <f>3600/G10</f>
         <v/>
       </c>
@@ -1782,19 +1853,19 @@
       <c r="D11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="22">
         <f>D11*$M$2</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="23">
         <f>3600/E11</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <f>$M$3</f>
         <v/>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="23">
         <f>3600/G11</f>
         <v/>
       </c>
@@ -1809,120 +1880,120 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="27" t="n">
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="26" t="n">
         <v>65.40000000000001</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="25">
         <f>3600/E13</f>
         <v/>
       </c>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>138 intervalos reales. mediana 65.4 s / media 61.7 / p25 41.6 / p75 71.6 / max 125. La hoja original indica 30 min.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>COMO SE LEE UNA FILA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Columnas B y C</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>Lo que decia la hoja original. Estan solo para comparar; no son medidas.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Ticks (columna D)</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="29" t="inlineStr">
         <is>
           <t>Cuantos despertares del aparato pasan entre una lectura de ese sensor y la siguiente. 3 = centinela (lo barato, cada rato); 90 = burst o lectura completa (todo, de tanto en tanto); 'excluido' = no se lee.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>Periodo NORMAL (E)</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B18" s="29" t="inlineStr">
         <is>
           <t>Es Ticks x 18.8 s. El 18.8 es lo que dura un despertar DE VERDAD, medido; en el programa pone 10 s. Esta en la celda M2.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t>Mediciones/h NORMAL (F)</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
+      <c r="B19" s="29" t="inlineStr">
         <is>
           <t>Son 3600 segundos de una hora, divididos entre el periodo.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>Periodo ALARMA (G)</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>24.9 s para todos. En alarma el aparato no duerme y repite la lectura completa sin parar, asi que ya no depende de los despertares. M3.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>Factor (columna I)</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B21" s="29" t="inlineStr">
         <is>
           <t>Cuantas veces mas a menudo se mide en alarma que en normal.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>EJEMPLO: la fila del CO2</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="31" t="inlineStr">
         <is>
           <t>Pone ticks = 90. Entonces: 90 despertares x 18.8 s = 1692 s, que son 28.2 minutos entre una medida de CO2 y la siguiente. Y 3600 / 1692 = 2.13 medidas por hora. En alarma pasa a 24.9 s, o sea 144.6 medidas por hora: 64 veces mas a menudo.</t>
         </is>
@@ -1963,96 +2034,96 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Placa</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Modulo C nodo 3 (C3), MAC 28:84:85:6F:82:88. Fecha 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>t activo por sensor</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Instrumentacion anadida al firmware: millis() alrededor de cada runSlot(), con una linea [t] por slot. Entorno medir-tiempos (SLEEP_ENABLED=0) para que cada pasada sea un burst completo y el puerto serie no desaparezca. 9 bursts; se toma la mediana.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Tick real</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Intervalos entre tramas STAT consecutivas de C3 en el log de Modulo B, divididos por el numero de despertares que declara el propio STAT. 37 intervalos en dos capturas independientes: 17.8 s y 18.1 s. Remedido a 18.8 s el 2026-10-08, al entrar el CO en el centinela.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Periodos normales</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Numero de ticks de cada contador (SENSOR_READ=3, BURST=90, LORA_TRANS=4) multiplicado por el tick real de 18.8 s. NO por los 10 s nominales.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Modo alarma</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Entorno medir-alarma (FORCE_ALARM_STATE=2). El nodo no duerme y repite el burst completo. Periodo medido entre bursts consecutivos: 24.9 s (11 bursts, 2026-10-07, con TX_KEEP_5V_RAIL).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Envio B -&gt; Modulo A</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Intervalos entre publicaciones AT+QMTPUB a v1/gateway/telemetry en 9 capturas de Modulo B del 5 y 6 de octubre. Se descartan los huecos &lt;5 s (publicaciones consecutivas del mismo evento) y &gt;600 s (reconexiones). n=138.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Lo que NO se ha medido aqui</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>Las corrientes. Requieren el PPK2 en el banco. Las medidas de corriente existentes estan en test_consumos/mediciones.csv, y dos contradicen la hoja: el SEN0466 consume 14.5 mA y no 5, y no tiene modo reposo (~15 mA siempre que este alimentado, no 0 uA).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Avisos</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>La hoja no incluye el ESP32-S3 (35 mA despierto, 0.026 mA dormido) ni la radio RYLR998 (50 mA en RX, 151 mA de pico en TX). A 47% de duty solo el ESP son ~16 mA de media, frente a ~1.4 mA de todos los sensores juntos.</t>
         </is>
